--- a/artfynd/A 34520-2025 artfynd.xlsx
+++ b/artfynd/A 34520-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127456657</v>
       </c>
       <c r="B2" t="n">
-        <v>91446</v>
+        <v>91450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34520-2025 artfynd.xlsx
+++ b/artfynd/A 34520-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127456657</v>
       </c>
       <c r="B2" t="n">
-        <v>91450</v>
+        <v>91452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34520-2025 artfynd.xlsx
+++ b/artfynd/A 34520-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127456657</v>
       </c>
       <c r="B2" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34520-2025 artfynd.xlsx
+++ b/artfynd/A 34520-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127456657</v>
       </c>
       <c r="B2" t="n">
-        <v>91458</v>
+        <v>91461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34520-2025 artfynd.xlsx
+++ b/artfynd/A 34520-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127456657</v>
       </c>
       <c r="B2" t="n">
-        <v>91461</v>
+        <v>91469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34520-2025 artfynd.xlsx
+++ b/artfynd/A 34520-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127456657</v>
       </c>
       <c r="B2" t="n">
-        <v>91469</v>
+        <v>91470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34520-2025 artfynd.xlsx
+++ b/artfynd/A 34520-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127456657</v>
       </c>
       <c r="B2" t="n">
-        <v>91470</v>
+        <v>91471</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34520-2025 artfynd.xlsx
+++ b/artfynd/A 34520-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127456657</v>
       </c>
       <c r="B2" t="n">
-        <v>91471</v>
+        <v>91472</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
